--- a/artfynd/A 14590-2026 artfynd.xlsx
+++ b/artfynd/A 14590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132820908</v>
       </c>
       <c r="B2" t="n">
-        <v>91941</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,14 +780,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132821032</v>
+        <v>132820844</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>793988</v>
+        <v>794075</v>
       </c>
       <c r="R3" t="n">
-        <v>7212061</v>
+        <v>7211851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hack högt upp i gammal tall</t>
+          <t>Gamla bohål i urgammal torraka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,14 +890,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132820976</v>
+        <v>132820884</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794133</v>
+        <v>794122</v>
       </c>
       <c r="R4" t="n">
-        <v>7212028</v>
+        <v>7212077</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>hål hackat i tall</t>
+          <t>hål hackade i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,27 +1000,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132821070</v>
+        <v>132820944</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>793974</v>
+        <v>794144</v>
       </c>
       <c r="R5" t="n">
-        <v>7212081</v>
+        <v>7212045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i gammeltall</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1110,14 +1110,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132820944</v>
+        <v>132820976</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>794144</v>
+        <v>794133</v>
       </c>
       <c r="R6" t="n">
-        <v>7212045</v>
+        <v>7212028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hål hackade i gammeltall</t>
+          <t>hål hackat i tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,14 +1220,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132820844</v>
+        <v>132821032</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1253,7 +1253,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794075</v>
+        <v>793988</v>
       </c>
       <c r="R7" t="n">
-        <v>7211851</v>
+        <v>7212061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gamla bohål i urgammal torraka</t>
+          <t>hack högt upp i gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132820884</v>
+        <v>132821070</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1363,7 +1363,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794122</v>
+        <v>793974</v>
       </c>
       <c r="R8" t="n">
-        <v>7212077</v>
+        <v>7212081</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,14 +1413,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hål hackade i tall</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1437,6 +1437,336 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132821118</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>793967</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7212073</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132821186</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>793983</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7212018</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132821321</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svarttjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>793962</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7212083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>bohål i död björk</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14590-2026 artfynd.xlsx
+++ b/artfynd/A 14590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132820844</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821118</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821186</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132821321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132820908</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132820884</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132820944</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,8 +1817,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132820976</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>